--- a/data/trans_dic/DC-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DC-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 17,75</t>
+          <t>9,78; 18,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,81</t>
+          <t>5,28; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 14,72</t>
+          <t>7,49; 14,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,08</t>
+          <t>9,2; 17,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 26,0</t>
+          <t>15,74; 26,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 31,9</t>
+          <t>20,97; 32,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,51; 31,19</t>
+          <t>20,67; 31,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 25,71</t>
+          <t>18,54; 26,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 20,45</t>
+          <t>13,94; 20,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 20,59</t>
+          <t>14,11; 20,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,48</t>
+          <t>14,91; 21,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,34; 19,9</t>
+          <t>14,4; 19,72</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,58; 25,92</t>
+          <t>18,63; 25,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,92</t>
+          <t>4,77; 9,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,7</t>
+          <t>4,2; 8,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,98; 23,77</t>
+          <t>15,04; 23,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,58; 49,15</t>
+          <t>40,63; 49,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 23,8</t>
+          <t>16,74; 23,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,06</t>
+          <t>8,44; 14,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,72; 41,25</t>
+          <t>33,76; 40,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,84; 36,83</t>
+          <t>30,63; 36,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,46; 15,92</t>
+          <t>11,33; 15,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 10,73</t>
+          <t>6,96; 10,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 31,21</t>
+          <t>25,2; 31,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,0</t>
+          <t>6,97; 13,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,42</t>
+          <t>5,64; 12,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,34</t>
+          <t>5,6; 11,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 27,55</t>
+          <t>18,89; 27,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 25,81</t>
+          <t>16,66; 25,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,4; 24,29</t>
+          <t>15,7; 25,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,61; 23,58</t>
+          <t>14,73; 24,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,4; 40,9</t>
+          <t>32,63; 41,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,02; 19,2</t>
+          <t>13,25; 18,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 17,22</t>
+          <t>11,89; 17,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,6</t>
+          <t>10,87; 16,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,07; 32,99</t>
+          <t>27,14; 33,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 24,59</t>
+          <t>16,57; 24,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 15,67</t>
+          <t>8,36; 15,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 14,58</t>
+          <t>7,88; 14,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 22,58</t>
+          <t>13,21; 22,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 26,33</t>
+          <t>17,48; 25,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 32,06</t>
+          <t>23,15; 32,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 29,18</t>
+          <t>19,6; 29,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 65,65</t>
+          <t>30,74; 64,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 24,13</t>
+          <t>17,87; 24,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,68; 22,59</t>
+          <t>16,42; 22,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 20,27</t>
+          <t>14,84; 20,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 51,97</t>
+          <t>25,01; 50,08</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,23</t>
+          <t>4,31; 11,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,49</t>
+          <t>11,88; 22,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,18</t>
+          <t>7,06; 15,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,61; 23,55</t>
+          <t>14,5; 23,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 24,84</t>
+          <t>13,58; 24,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,27; 46,31</t>
+          <t>32,82; 45,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,0; 25,32</t>
+          <t>14,82; 25,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 36,29</t>
+          <t>14,26; 36,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 16,85</t>
+          <t>10,01; 16,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,07; 33,1</t>
+          <t>23,91; 32,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 19,1</t>
+          <t>11,98; 19,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,04; 28,63</t>
+          <t>16,89; 28,79</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,21; 21,03</t>
+          <t>12,3; 21,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 19,99</t>
+          <t>11,19; 20,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 14,29</t>
+          <t>6,93; 14,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,37</t>
+          <t>24,02; 33,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 32,58</t>
+          <t>22,27; 32,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,77; 32,75</t>
+          <t>22,16; 32,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,13; 20,2</t>
+          <t>11,02; 20,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,03; 48,9</t>
+          <t>38,94; 48,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,5; 25,36</t>
+          <t>18,47; 25,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,92; 24,93</t>
+          <t>17,88; 24,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,12</t>
+          <t>9,78; 15,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,44; 39,18</t>
+          <t>32,86; 39,27</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,83; 19,71</t>
+          <t>13,48; 19,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,79</t>
+          <t>9,76; 15,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,83</t>
+          <t>8,59; 13,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,02; 35,69</t>
+          <t>26,91; 35,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,34; 23,74</t>
+          <t>17,28; 23,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,2; 30,07</t>
+          <t>23,22; 30,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,46; 25,12</t>
+          <t>18,62; 25,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,21; 82,22</t>
+          <t>54,85; 83,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,06; 20,35</t>
+          <t>16,13; 20,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,15; 21,74</t>
+          <t>17,29; 21,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,7</t>
+          <t>14,62; 18,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,17; 70,68</t>
+          <t>43,08; 69,07</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,42</t>
+          <t>19,11; 25,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,82</t>
+          <t>6,78; 10,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,96</t>
+          <t>7,52; 11,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,14; 20,06</t>
+          <t>6,38; 20,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,4; 37,58</t>
+          <t>30,68; 37,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,7</t>
+          <t>14,95; 20,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,94; 18,14</t>
+          <t>12,92; 17,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,94; 35,96</t>
+          <t>29,78; 35,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,16; 30,62</t>
+          <t>25,93; 30,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,2</t>
+          <t>11,63; 15,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,95; 14,44</t>
+          <t>10,91; 14,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,07; 26,74</t>
+          <t>13,48; 26,83</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,25; 18,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,45</t>
+          <t>9,39; 11,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,43; 10,62</t>
+          <t>8,48; 10,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,37</t>
+          <t>15,66; 22,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,44; 29,57</t>
+          <t>26,28; 29,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,34</t>
+          <t>22,35; 25,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,61</t>
+          <t>17,1; 19,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,77; 52,97</t>
+          <t>37,87; 52,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,79</t>
+          <t>21,75; 23,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16,24; 18,14</t>
+          <t>16,34; 18,24</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13,14; 14,85</t>
+          <t>13,19; 14,88</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,45; 38,85</t>
+          <t>28,53; 37,95</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26227; 48454</t>
+          <t>26698; 49324</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16233; 34801</t>
+          <t>15571; 34675</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20616; 43228</t>
+          <t>21997; 43566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28800; 53205</t>
+          <t>28641; 53601</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41704; 67820</t>
+          <t>41065; 67846</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58887; 91642</t>
+          <t>60234; 92467</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59212; 90037</t>
+          <t>59678; 90447</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53095; 74458</t>
+          <t>53712; 76387</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74562; 109193</t>
+          <t>74411; 107885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81130; 119859</t>
+          <t>82112; 120539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88346; 125129</t>
+          <t>86825; 126071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86207; 119614</t>
+          <t>86563; 118534</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91593; 127787</t>
+          <t>91843; 128141</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24431; 50128</t>
+          <t>24114; 49076</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20861; 43705</t>
+          <t>21122; 42246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77677; 123201</t>
+          <t>77945; 119902</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>204504; 247688</t>
+          <t>204775; 248512</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87560; 124651</t>
+          <t>87664; 125587</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44327; 73537</t>
+          <t>44137; 74935</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>173668; 212404</t>
+          <t>173863; 211007</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>307528; 367236</t>
+          <t>305420; 364709</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>117908; 163867</t>
+          <t>116635; 162914</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71156; 110027</t>
+          <t>71396; 108293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>260606; 322548</t>
+          <t>260368; 322365</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23034; 44629</t>
+          <t>22212; 44043</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18964; 40241</t>
+          <t>18292; 39197</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17073; 36137</t>
+          <t>17842; 36293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58830; 87078</t>
+          <t>59695; 88427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58232; 86572</t>
+          <t>55885; 86347</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52522; 82847</t>
+          <t>53532; 85943</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49125; 79303</t>
+          <t>49539; 81735</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113113; 142809</t>
+          <t>113934; 143724</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85188; 125595</t>
+          <t>86693; 123364</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77906; 114523</t>
+          <t>79093; 116138</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72414; 108742</t>
+          <t>71189; 106936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>180061; 219418</t>
+          <t>180531; 221853</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57558; 88209</t>
+          <t>59437; 88410</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32047; 58616</t>
+          <t>31253; 57136</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28697; 53951</t>
+          <t>29135; 54905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41499; 70569</t>
+          <t>41304; 70290</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65313; 97798</t>
+          <t>64942; 96445</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89268; 124684</t>
+          <t>90023; 125479</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77652; 112993</t>
+          <t>75891; 113241</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>143969; 312301</t>
+          <t>146216; 307145</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132732; 176215</t>
+          <t>130494; 176594</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127252; 172380</t>
+          <t>125243; 172230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>110642; 153503</t>
+          <t>112387; 155176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>192657; 409628</t>
+          <t>197114; 394728</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8412; 22832</t>
+          <t>8768; 23910</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24912; 47814</t>
+          <t>25251; 47924</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14704; 34182</t>
+          <t>14918; 33719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26122; 42091</t>
+          <t>25921; 42608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29433; 51587</t>
+          <t>28200; 51546</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73061; 101691</t>
+          <t>72072; 100784</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32795; 55352</t>
+          <t>32389; 56187</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37830; 93917</t>
+          <t>36900; 93444</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40037; 69259</t>
+          <t>41127; 69296</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104025; 143047</t>
+          <t>103348; 140596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52949; 82102</t>
+          <t>51496; 81925</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70181; 125245</t>
+          <t>73895; 125950</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33078; 56955</t>
+          <t>33300; 56949</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30855; 54769</t>
+          <t>30657; 55038</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17286; 37592</t>
+          <t>18230; 37462</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63999; 89991</t>
+          <t>64766; 90370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60253; 90623</t>
+          <t>61940; 90810</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60951; 91703</t>
+          <t>62069; 92104</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30386; 55166</t>
+          <t>30109; 56044</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100317; 125695</t>
+          <t>100086; 125515</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101565; 139191</t>
+          <t>101406; 138193</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99292; 138131</t>
+          <t>99055; 137872</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53396; 86439</t>
+          <t>52418; 84645</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>170867; 206370</t>
+          <t>173069; 206823</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85046; 121223</t>
+          <t>82877; 118422</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64136; 98015</t>
+          <t>64673; 99498</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55906; 90820</t>
+          <t>56420; 89199</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168655; 222832</t>
+          <t>168011; 220219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>110684; 151538</t>
+          <t>110266; 149108</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>160980; 208619</t>
+          <t>161095; 209290</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>127605; 173686</t>
+          <t>128731; 173717</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>468917; 698234</t>
+          <t>465836; 706131</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>201285; 255093</t>
+          <t>202172; 257605</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>232655; 294995</t>
+          <t>234540; 294045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>196876; 252069</t>
+          <t>197013; 254986</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>636130; 1041515</t>
+          <t>634767; 1017705</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>143755; 189099</t>
+          <t>142166; 187783</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>52064; 84281</t>
+          <t>52841; 85106</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>59322; 93108</t>
+          <t>58580; 90583</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>57021; 186332</t>
+          <t>59251; 187364</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>238153; 294446</t>
+          <t>240385; 292012</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>125679; 170533</t>
+          <t>123152; 168917</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>106917; 149893</t>
+          <t>106722; 148529</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>214904; 258074</t>
+          <t>213723; 254737</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>399488; 467590</t>
+          <t>396001; 464780</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>187139; 243669</t>
+          <t>186407; 243264</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>175669; 231665</t>
+          <t>175064; 226888</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>231666; 440292</t>
+          <t>221953; 441777</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>534641; 619071</t>
+          <t>532336; 618642</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>322100; 392294</t>
+          <t>321648; 393929</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>286053; 360552</t>
+          <t>287743; 357414</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>558646; 774040</t>
+          <t>541691; 774077</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>893553; 999137</t>
+          <t>887963; 995197</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>798128; 901736</t>
+          <t>795179; 899494</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>600473; 694991</t>
+          <t>606242; 705030</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1402061; 1966429</t>
+          <t>1405779; 1954309</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1444561; 1583231</t>
+          <t>1447744; 1578929</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1134634; 1266868</t>
+          <t>1141083; 1274004</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>911753; 1030591</t>
+          <t>915013; 1032720</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2040610; 2786276</t>
+          <t>2046408; 2721471</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DC-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 18,07</t>
+          <t>9,86; 17,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,76</t>
+          <t>5,07; 11,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 14,83</t>
+          <t>7,16; 14,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 17,21</t>
+          <t>9,46; 16,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,74; 26,01</t>
+          <t>15,9; 26,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,97; 32,19</t>
+          <t>20,8; 32,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,67; 31,33</t>
+          <t>20,76; 31,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 26,37</t>
+          <t>18,61; 25,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 20,21</t>
+          <t>13,79; 20,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 20,71</t>
+          <t>13,72; 20,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 21,64</t>
+          <t>14,98; 21,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,72</t>
+          <t>14,91; 20,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,63; 25,99</t>
+          <t>18,58; 26,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,71</t>
+          <t>4,77; 9,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,41</t>
+          <t>4,36; 8,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,04; 23,13</t>
+          <t>15,54; 23,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,63; 49,31</t>
+          <t>40,45; 49,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 23,98</t>
+          <t>16,55; 23,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,33</t>
+          <t>8,56; 14,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,76; 40,97</t>
+          <t>33,21; 40,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,63; 36,58</t>
+          <t>30,59; 36,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,83</t>
+          <t>11,47; 15,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,56</t>
+          <t>7,03; 10,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,2; 31,2</t>
+          <t>25,18; 30,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,81</t>
+          <t>6,81; 14,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 12,1</t>
+          <t>5,82; 12,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 11,39</t>
+          <t>5,37; 11,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,89; 27,98</t>
+          <t>19,09; 27,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 25,74</t>
+          <t>17,19; 26,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 25,2</t>
+          <t>15,59; 24,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 24,3</t>
+          <t>14,72; 23,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,63; 41,17</t>
+          <t>33,34; 41,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 18,86</t>
+          <t>13,02; 18,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,89; 17,46</t>
+          <t>11,83; 17,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 16,33</t>
+          <t>11,03; 16,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,14; 33,35</t>
+          <t>27,38; 33,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 24,65</t>
+          <t>16,05; 24,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 15,28</t>
+          <t>8,43; 15,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,84</t>
+          <t>7,53; 14,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,21; 22,49</t>
+          <t>11,71; 20,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 25,96</t>
+          <t>17,86; 25,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,15; 32,26</t>
+          <t>22,99; 32,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 29,24</t>
+          <t>19,59; 28,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,74; 64,56</t>
+          <t>31,26; 39,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,19</t>
+          <t>17,91; 23,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,42; 22,57</t>
+          <t>16,69; 22,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,49</t>
+          <t>14,92; 20,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 50,08</t>
+          <t>22,77; 28,88</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,76</t>
+          <t>4,29; 11,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,88; 22,54</t>
+          <t>11,78; 22,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 15,96</t>
+          <t>7,11; 15,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,5; 23,84</t>
+          <t>14,17; 23,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 24,82</t>
+          <t>14,42; 25,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,82; 45,9</t>
+          <t>32,37; 45,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 25,7</t>
+          <t>15,27; 25,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,26; 36,11</t>
+          <t>29,5; 38,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,86</t>
+          <t>9,99; 17,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,91; 32,53</t>
+          <t>23,89; 32,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,06</t>
+          <t>12,13; 19,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 28,79</t>
+          <t>23,34; 29,63</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 21,03</t>
+          <t>12,32; 21,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,19; 20,09</t>
+          <t>10,85; 19,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,24</t>
+          <t>6,45; 14,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 33,52</t>
+          <t>23,47; 32,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,27; 32,65</t>
+          <t>21,58; 32,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,16; 32,89</t>
+          <t>21,46; 32,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 20,52</t>
+          <t>11,51; 20,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38,94; 48,83</t>
+          <t>38,6; 48,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 25,17</t>
+          <t>18,38; 25,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,88; 24,89</t>
+          <t>17,88; 24,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,79</t>
+          <t>9,99; 15,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,86; 39,27</t>
+          <t>32,29; 39,14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,48; 19,25</t>
+          <t>13,44; 19,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,01</t>
+          <t>9,69; 14,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,59</t>
+          <t>8,57; 13,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,91; 35,28</t>
+          <t>27,17; 35,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 23,36</t>
+          <t>17,05; 23,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,22; 30,16</t>
+          <t>22,99; 30,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,62; 25,13</t>
+          <t>18,66; 24,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,85; 83,15</t>
+          <t>53,53; 60,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,13; 20,55</t>
+          <t>16,2; 20,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,29; 21,67</t>
+          <t>17,13; 21,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,62; 18,92</t>
+          <t>14,44; 18,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,08; 69,07</t>
+          <t>41,64; 46,93</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,11; 25,25</t>
+          <t>19,43; 25,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,92</t>
+          <t>6,83; 11,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,63</t>
+          <t>7,55; 11,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,38; 20,17</t>
+          <t>16,15; 21,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,68; 37,27</t>
+          <t>30,27; 36,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,95; 20,5</t>
+          <t>15,31; 20,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,92; 17,98</t>
+          <t>12,7; 17,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,78; 35,49</t>
+          <t>29,42; 35,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,93; 30,43</t>
+          <t>25,55; 30,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,63; 15,18</t>
+          <t>11,59; 15,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 14,14</t>
+          <t>10,88; 14,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,48; 26,83</t>
+          <t>23,5; 27,3</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,25; 18,88</t>
+          <t>16,27; 19,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,39; 11,5</t>
+          <t>9,21; 11,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,48; 10,53</t>
+          <t>8,54; 10,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,66; 22,37</t>
+          <t>20,0; 23,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,28; 29,45</t>
+          <t>26,41; 29,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,35; 25,28</t>
+          <t>22,37; 25,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,1; 19,89</t>
+          <t>17,06; 19,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>37,87; 52,64</t>
+          <t>37,36; 40,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21,75; 23,72</t>
+          <t>21,63; 23,74</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,24</t>
+          <t>16,26; 18,17</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13,19; 14,88</t>
+          <t>13,27; 14,91</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,53; 37,95</t>
+          <t>29,32; 31,43</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>40364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63754</t>
+          <t>69172</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>102377</t>
+          <t>109536</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26698; 49324</t>
+          <t>26912; 48266</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15571; 34675</t>
+          <t>14943; 33617</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21997; 43566</t>
+          <t>21030; 43619</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28641; 53601</t>
+          <t>30163; 53273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41065; 67846</t>
+          <t>41475; 68490</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60234; 92467</t>
+          <t>59756; 92932</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59678; 90447</t>
+          <t>59923; 90088</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>53712; 76387</t>
+          <t>58822; 81647</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74411; 107885</t>
+          <t>73615; 109358</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82112; 120539</t>
+          <t>79869; 118358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86825; 126071</t>
+          <t>87243; 124741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86563; 118534</t>
+          <t>94676; 127405</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98130</t>
+          <t>101952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>191775</t>
+          <t>201154</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>289905</t>
+          <t>303105</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91843; 128141</t>
+          <t>91617; 128224</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24114; 49076</t>
+          <t>24111; 48335</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21122; 42246</t>
+          <t>21933; 43542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77945; 119902</t>
+          <t>82475; 125685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>204775; 248512</t>
+          <t>203826; 249436</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87664; 125587</t>
+          <t>86699; 123708</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44137; 74935</t>
+          <t>44779; 74703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>173863; 211007</t>
+          <t>181468; 221696</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>305420; 364709</t>
+          <t>304948; 364641</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116635; 162914</t>
+          <t>118086; 163101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71396; 108293</t>
+          <t>72099; 106211</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>260368; 322365</t>
+          <t>271250; 332071</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71830</t>
+          <t>72070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>132586</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>199497</t>
+          <t>204657</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22212; 44043</t>
+          <t>21705; 45760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18292; 39197</t>
+          <t>18856; 39590</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17842; 36293</t>
+          <t>17099; 36800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59695; 88427</t>
+          <t>60311; 87644</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55885; 86347</t>
+          <t>57654; 88058</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53532; 85943</t>
+          <t>53167; 83335</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49539; 81735</t>
+          <t>49518; 80598</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113934; 143724</t>
+          <t>118813; 147701</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86693; 123364</t>
+          <t>85213; 123477</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79093; 116138</t>
+          <t>78698; 115454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71189; 106936</t>
+          <t>72254; 107910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>180531; 221853</t>
+          <t>184081; 224469</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>58210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>202307</t>
+          <t>148137</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>257038</t>
+          <t>206347</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59437; 88410</t>
+          <t>57567; 88359</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31253; 57136</t>
+          <t>31532; 56769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29135; 54905</t>
+          <t>27857; 53217</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41304; 70290</t>
+          <t>43700; 75703</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>64942; 96445</t>
+          <t>66355; 95307</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90023; 125479</t>
+          <t>89414; 124798</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75891; 113241</t>
+          <t>75867; 111305</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>146216; 307145</t>
+          <t>131895; 167080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130494; 176594</t>
+          <t>130761; 174657</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125243; 172230</t>
+          <t>127347; 172892</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112387; 155176</t>
+          <t>112964; 155262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>197114; 394728</t>
+          <t>181012; 229655</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>37002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73005</t>
+          <t>77494</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>106367</t>
+          <t>114496</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8768; 23910</t>
+          <t>8727; 23575</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25251; 47924</t>
+          <t>25045; 47519</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14918; 33719</t>
+          <t>15019; 32127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25921; 42608</t>
+          <t>29149; 47825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28200; 51546</t>
+          <t>29954; 52403</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72072; 100784</t>
+          <t>71073; 100296</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32389; 56187</t>
+          <t>33368; 56786</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36900; 93444</t>
+          <t>67535; 88086</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41127; 69296</t>
+          <t>41064; 70287</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103348; 140596</t>
+          <t>103258; 142205</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51496; 81925</t>
+          <t>52137; 83250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73895; 125950</t>
+          <t>101418; 128752</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77078</t>
+          <t>75694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>114616</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>189236</t>
+          <t>190309</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33300; 56949</t>
+          <t>33359; 57696</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30657; 55038</t>
+          <t>29725; 54516</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18230; 37462</t>
+          <t>16981; 37578</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64766; 90370</t>
+          <t>63540; 86907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61940; 90810</t>
+          <t>60017; 90478</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62069; 92104</t>
+          <t>60092; 90290</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30109; 56044</t>
+          <t>31441; 56231</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100086; 125515</t>
+          <t>101810; 127276</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101406; 138193</t>
+          <t>100916; 139379</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>99055; 137872</t>
+          <t>99035; 136973</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52418; 84645</t>
+          <t>53561; 84867</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>173069; 206823</t>
+          <t>172562; 209165</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194307</t>
+          <t>224290</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>567108</t>
+          <t>439176</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>761415</t>
+          <t>663466</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>82877; 118422</t>
+          <t>82656; 117442</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64673; 99498</t>
+          <t>64226; 98459</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56420; 89199</t>
+          <t>56283; 89819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168011; 220219</t>
+          <t>195559; 252309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>110266; 149108</t>
+          <t>108802; 150201</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>161095; 209290</t>
+          <t>159488; 209062</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>128731; 173717</t>
+          <t>128988; 172259</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>465836; 706131</t>
+          <t>413244; 466159</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>202172; 257605</t>
+          <t>203007; 261008</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>234540; 294045</t>
+          <t>232385; 294009</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>197013; 254986</t>
+          <t>194655; 248900</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>634767; 1017705</t>
+          <t>621189; 700146</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130630</t>
+          <t>147829</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>234398</t>
+          <t>266531</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>365028</t>
+          <t>414360</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>142166; 187783</t>
+          <t>144508; 190700</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>52841; 85106</t>
+          <t>53236; 86862</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>58580; 90583</t>
+          <t>58760; 91836</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>59251; 187364</t>
+          <t>128911; 170482</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>240385; 292012</t>
+          <t>237198; 289551</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>123152; 168917</t>
+          <t>126095; 170143</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>106722; 148529</t>
+          <t>104926; 147795</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>213723; 254737</t>
+          <t>244578; 291108</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>396001; 464780</t>
+          <t>390264; 462003</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>186407; 243264</t>
+          <t>185803; 242782</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>175064; 226888</t>
+          <t>174608; 227254</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>221953; 441777</t>
+          <t>382868; 444794</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>698690</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1572173</t>
+          <t>1448866</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2270863</t>
+          <t>2206276</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>532336; 618642</t>
+          <t>533223; 622922</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>321648; 393929</t>
+          <t>315704; 391960</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>287743; 357414</t>
+          <t>289786; 359789</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>541691; 774077</t>
+          <t>706662; 812902</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>887963; 995197</t>
+          <t>892353; 999527</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>795179; 899494</t>
+          <t>795910; 895993</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>606242; 705030</t>
+          <t>604553; 701740</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1405779; 1954309</t>
+          <t>1396088; 1501379</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1447744; 1578929</t>
+          <t>1439946; 1579800</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1141083; 1274004</t>
+          <t>1135931; 1268886</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>915013; 1032720</t>
+          <t>920510; 1034593</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2046408; 2721471</t>
+          <t>2131668; 2284908</t>
         </is>
       </c>
     </row>
